--- a/winner_final/data/football_all.xlsx
+++ b/winner_final/data/football_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\winner_final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D1CF7-8522-4154-9913-7C087F3FABED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB5639A-81CA-41DD-B6C4-F63AE2020A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="-14640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4755" yWindow="1755" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
   <si>
     <t>Team</t>
   </si>
@@ -233,9 +233,6 @@
     <t>צ'לסי</t>
   </si>
   <si>
-    <t>ברנטפורד </t>
-  </si>
-  <si>
     <t>אסטון וילה</t>
   </si>
   <si>
@@ -288,6 +285,18 @@
   </si>
   <si>
     <t>פולהאם</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>ברנטפורד</t>
   </si>
 </sst>
 </file>
@@ -337,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -359,6 +368,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -641,14 +653,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.875" customWidth="1"/>
     <col min="2" max="3" width="29.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -658,8 +670,11 @@
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -667,8 +682,11 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>40</v>
       </c>
@@ -676,8 +694,11 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
@@ -685,8 +706,11 @@
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>42</v>
       </c>
@@ -694,8 +718,11 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -703,8 +730,11 @@
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -712,8 +742,11 @@
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>25</v>
       </c>
@@ -721,8 +754,11 @@
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>31</v>
       </c>
@@ -730,8 +766,11 @@
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
@@ -739,8 +778,11 @@
       <c r="C10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
@@ -748,8 +790,11 @@
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
@@ -757,8 +802,11 @@
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>32</v>
       </c>
@@ -766,8 +814,11 @@
       <c r="C13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>33</v>
       </c>
@@ -775,8 +826,11 @@
       <c r="C14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -784,8 +838,11 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -793,8 +850,11 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
@@ -802,197 +862,289 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="D40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
         <v>62</v>
+      </c>
+      <c r="D41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="6"/>
+      <c r="D43" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
